--- a/data/trans_dic/IP31KM03_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,38; 94,32</t>
+          <t>73,19; 90,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,42; 90,98</t>
+          <t>81,2; 94,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,78; 90,73</t>
+          <t>80,51; 91,75</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,94; 89,58</t>
+          <t>81,96; 91,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,8; 91,13</t>
+          <t>81,6; 90,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,04; 89,47</t>
+          <t>83,56; 89,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,96%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,49; 91,4</t>
+          <t>80,18; 89,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,45; 89,27</t>
+          <t>81,41; 90,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,7; 89,05</t>
+          <t>82,56; 88,65</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77,55; 87,92</t>
+          <t>75,5; 84,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75,65; 85,22</t>
+          <t>75,97; 84,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,14; 85,03</t>
+          <t>76,77; 83,09</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,79%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>82,04; 87,31</t>
+          <t>80,68; 85,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>80,89; 86,24</t>
+          <t>81,56; 86,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,36; 86,07</t>
+          <t>82,03; 85,62</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41501</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79213</t>
+          <t>69519</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37372; 43854</t>
+          <t>27397; 33971</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33247; 41200</t>
+          <t>34657; 40339</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73224; 83274</t>
+          <t>64500; 73507</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>223</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>136584</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>158750</t>
+          <t>125998</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>294848</t>
+          <t>262582</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>127351; 142701</t>
+          <t>128712; 143403</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>150663; 165813</t>
+          <t>118741; 131929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>283380; 305327</t>
+          <t>252811; 270955</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>203</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>150633</t>
+          <t>170545</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>181397</t>
+          <t>151622</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>332032</t>
+          <t>322167</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>142768; 158188</t>
+          <t>160459; 178283</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>170954; 189698</t>
+          <t>142198; 158407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>318870; 343339</t>
+          <t>309448; 332274</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>270</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>225272</t>
+          <t>235192</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>246193</t>
+          <t>204004</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>471465</t>
+          <t>439196</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>212704; 241129</t>
+          <t>220639; 247923</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>230734; 259923</t>
+          <t>193989; 215393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>452625; 492566</t>
+          <t>420349; 454956</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>769</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>553504</t>
+          <t>573722</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519742</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1177558</t>
+          <t>1093463</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>535855; 570235</t>
+          <t>554146; 590560</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>602396; 642254</t>
+          <t>504214; 534529</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1151284; 1203148</t>
+          <t>1070568; 1117360</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM03_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman verduras frescas o cocinadas una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>83,88%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>73,19; 90,75</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>81,2; 94,51</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80,51; 91,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>86,59%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>81,96; 91,32</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>81,6; 90,66</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>83,56; 89,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>80,18; 89,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>81,41; 90,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>82,56; 88,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>80,48%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>79,9%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>75,5; 84,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>75,97; 84,36</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>76,77; 83,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>83,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>80,68; 85,98</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>81,56; 86,46</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>82,03; 85,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8388067235746336</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.8930980736528902</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8677297682666264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>31401</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>38118</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>69519</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7318623012236156</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8119976355596243</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8050831372491335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>27397; 33971</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>34657; 40339</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>64500; 73507</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9074635713398245</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9451228441309998</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9175052320390861</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8697280720226148</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8658608181133848</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.867868096140842</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>136584</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>125998</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>262582</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8196028130638636</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8159858740104972</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8355736174536226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>128712; 143403</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>118741; 131929</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>252811; 270955</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9131528891811868</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9066132555575542</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8955410472205466</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8521898754123507</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8680380523213943</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.859575817635144</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>170545</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>151622</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>322167</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.801788734327389</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8140845331066086</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.825639435026134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>160459; 178283</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>142198; 158407</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>309448; 332274</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8908551369346442</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9068845556550976</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8865428761846342</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8048437502758218</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.7989580280624129</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8020991212391096</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>235192</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>204004</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>439196</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.7550406800155089</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.75973874461366</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.7676787587274778</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>220639; 247923</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>193989; 215393</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>420349; 454956</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8484080111829759</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.843565121146315</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8308813134873305</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1553</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8353263234292188</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8407236993244187</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.837883119632662</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>573722</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>519742</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1093463</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8068234038599538</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8156049540271836</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.820339059425935</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>554146; 590560</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>504214; 534529</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1070568; 1117360</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8598411009676892</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8646425858888755</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.856194125313137</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman verduras frescas o cocinadas una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>31401</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>38118</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>69519</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>27397</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>34657</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>64500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>33971</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>40339</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>73507</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>238</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>136584</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>125998</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>262582</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>128712</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>118741</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>252811</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>143403</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>131929</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>270955</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>170545</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>151622</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>322167</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>160459</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>142198</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>309448</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>178283</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>158407</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>332274</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>272</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>235192</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>204004</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>439196</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>220639</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>193989</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>420349</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>247923</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>215393</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>454956</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>784</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>769</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>573722</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>519742</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1093463</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>554146</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>504214</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1070568</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>590560</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>534529</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1117360</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>